--- a/RACKS C12.xlsx
+++ b/RACKS C12.xlsx
@@ -1078,7 +1078,7 @@
     <t>SDI IN</t>
   </si>
   <si>
-    <t>Distribuidor PGM (cam pvw)</t>
+    <t>Distribuidor PGM (cam pvw test)</t>
   </si>
   <si>
     <t>7</t>
